--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>blue-light</t>
+          <t>orange</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.02</t>
+          <t>v0.03</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -1633,7 +1633,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.03</t>
+          <t>v0.05</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.05</t>
+          <t>v0.06</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.06</t>
+          <t>v0.07</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.07</t>
+          <t>v0.08</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.08</t>
+          <t>v0.09</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.09</t>
+          <t>v0.10</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.10</t>
+          <t>v0.11</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>v0.11</t>
+          <t>v0.12</t>
         </is>
       </c>
     </row>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdemmler\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{221D5CB6-11C7-4310-AD6E-474AA489FDCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D44938-C56F-418B-8ECC-D10009CF0FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="247">
   <si>
     <t>id</t>
   </si>
@@ -684,9 +684,6 @@
     <t>Executive</t>
   </si>
   <si>
-    <t>exec</t>
-  </si>
-  <si>
     <t>Events, Programming, and Sales</t>
   </si>
   <si>
@@ -756,16 +753,16 @@
     <t>directoryDate</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
-  </si>
-  <si>
     <t>version</t>
   </si>
   <si>
-    <t>v0.09</t>
-  </si>
-  <si>
-    <t>Short Job Description can be added here…</t>
+    <t>v0.14</t>
+  </si>
+  <si>
+    <t>Short Job Description can be added here...</t>
+  </si>
+  <si>
+    <t>red</t>
   </si>
 </sst>
 </file>
@@ -831,7 +828,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -845,6 +842,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1228,7 +1226,7 @@
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2156,7 +2154,7 @@
         <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2164,10 +2162,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2175,10 +2173,10 @@
         <v>95</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2186,10 +2184,10 @@
         <v>131</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2197,10 +2195,10 @@
         <v>146</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2208,10 +2206,10 @@
         <v>210</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2230,66 +2228,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
+      </c>
+      <c r="B7" s="7">
+        <v>46204</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/staff-data.xlsx
+++ b/staff-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdemmler\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdemmler\Downloads\tms-org-chart-v0.14_2\tms-org-chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D44938-C56F-418B-8ECC-D10009CF0FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FDDB49-842D-459D-A3AD-EB1E78DF21A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="248">
   <si>
     <t>id</t>
   </si>
@@ -684,6 +684,9 @@
     <t>Executive</t>
   </si>
   <si>
+    <t>exec</t>
+  </si>
+  <si>
     <t>Events, Programming, and Sales</t>
   </si>
   <si>
@@ -759,10 +762,10 @@
     <t>v0.14</t>
   </si>
   <si>
-    <t>Short Job Description can be added here...</t>
-  </si>
-  <si>
-    <t>red</t>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>Short Descriptions can be added to all staff or leave blank…</t>
   </si>
 </sst>
 </file>
@@ -842,7 +845,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1226,7 +1229,7 @@
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2154,7 +2157,7 @@
         <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2162,10 +2165,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2173,10 +2176,10 @@
         <v>95</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2184,10 +2187,10 @@
         <v>131</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2195,10 +2198,10 @@
         <v>146</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2206,10 +2209,10 @@
         <v>210</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2228,66 +2231,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="7">
-        <v>46204</v>
+        <v>243</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
